--- a/1Corr_RevGrades.xlsx
+++ b/1Corr_RevGrades.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\Training\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B8667D-4319-42AE-844C-ED5CBC389592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81FC431-1993-40CD-B694-ABB2318BA47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,10 +108,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -432,7 +436,8 @@
   <dimension ref="A1:F214"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.21875" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
   </cols>
@@ -452,7 +457,7 @@
       <c r="B2">
         <v>83.49</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
